--- a/plantillas/05_IndicadoresPDM.xlsx
+++ b/plantillas/05_IndicadoresPDM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\municipio-inversiones\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E2AD2C-EF32-40D9-AD41-2728594854A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8066637-ECBF-4253-AAD8-BE9AD97C1298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -866,7 +866,7 @@
         <v>108</v>
       </c>
       <c r="C2" s="3">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -883,7 +883,7 @@
         <v>109</v>
       </c>
       <c r="C3" s="5">
-        <v>15</v>
+        <v>52.6</v>
       </c>
       <c r="D3" s="5">
         <v>100</v>
@@ -900,7 +900,7 @@
         <v>110</v>
       </c>
       <c r="C4" s="3">
-        <v>42</v>
+        <v>44.6</v>
       </c>
       <c r="D4" s="3">
         <v>100</v>
@@ -917,7 +917,7 @@
         <v>111</v>
       </c>
       <c r="C5" s="5">
-        <v>35</v>
+        <v>55.2</v>
       </c>
       <c r="D5" s="5">
         <v>100</v>
